--- a/output/pdf_financials_xlsx/ALDE.xlsx
+++ b/output/pdf_financials_xlsx/ALDE.xlsx
@@ -3358,25 +3358,25 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.124998</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.356775</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.246012</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.45102</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>3.773333</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>4.541223</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>8.172014000000001</v>
       </c>
     </row>
     <row r="93">
@@ -4140,16 +4140,16 @@
         <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-32.258061</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-3.632496</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-5.848089</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-9.846738999999999</v>
       </c>
       <c r="G118" s="3" t="n">
         <v>0</v>
@@ -5752,7 +5752,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -6542,7 +6546,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -7198,7 +7206,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -9488,7 +9500,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ALDE.xlsx
+++ b/output/pdf_financials_xlsx/ALDE.xlsx
@@ -792,16 +792,16 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.024838</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.047161</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.009381</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.014103</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0.27276</v>
@@ -1297,16 +1297,16 @@
         <v>-0.544216</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.544216</v>
+        <v>-0.5690539999999999</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.922582</v>
+        <v>-1.969743</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.743774</v>
+        <v>-1.753155</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.636719</v>
+        <v>-0.650822</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-2.644846</v>
@@ -1359,16 +1359,16 @@
         <v>-0.544216</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.544216</v>
+        <v>-0.5690539999999999</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.922582</v>
+        <v>-1.969743</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.743774</v>
+        <v>-1.753155</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.636719</v>
+        <v>-0.650822</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-2.644846</v>
@@ -1519,16 +1519,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>5.163303</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.505569</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>7.285359</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0.634944</v>
@@ -1581,16 +1581,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>5.163303</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.030408</v>
+        <v>0.535977</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.047505</v>
+        <v>7.332864</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0.663977</v>
@@ -1953,16 +1953,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1e-06</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>5.182702</v>
+        <v>0.019399</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.515347</v>
+        <v>0.009778</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>7.335089</v>
+        <v>0.04973</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.050068</v>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
@@ -14652,7 +14652,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">

--- a/output/pdf_financials_xlsx/ALDE.xlsx
+++ b/output/pdf_financials_xlsx/ALDE.xlsx
@@ -3892,13 +3892,13 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.027805</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.070628</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="F110" s="3" t="n">
         <v>0</v>
@@ -3907,10 +3907,10 @@
         <v>0</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.31387</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.000714</v>
       </c>
     </row>
     <row r="111">
@@ -7474,7 +7474,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -7674,7 +7678,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
